--- a/SuppXLS/Demands/ScenDem_DEM_Ref.xlsx
+++ b/SuppXLS/Demands/ScenDem_DEM_Ref.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261020\SuppXLS\Demands\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\Demands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C296F96-C5D1-4D45-9FA7-67B6EDBB8799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA0978-26BE-4C32-B04F-6B9AF4AAD307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -74,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>GDP</t>
   </si>
@@ -194,13 +207,22 @@
   </si>
   <si>
     <t>~DRVR_Scenario: : DEM_Ref</t>
+  </si>
+  <si>
+    <t>pop</t>
+  </si>
+  <si>
+    <t>gdp</t>
+  </si>
+  <si>
+    <t>gdpp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -238,6 +260,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -266,7 +294,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -277,6 +305,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -733,35 +763,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AG25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
       <c r="C3" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="C5" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +889,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -869,95 +899,124 @@
       <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="9">
+        <f>D7+E24</f>
         <v>1.0512990110773976</v>
       </c>
-      <c r="F7" s="3">
-        <v>1.10394102645472</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1.1703520716072517</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1.2329579589421567</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1.2699466977104215</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1.3207445656188384</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1.3828195602029236</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1.4533433577732726</v>
-      </c>
-      <c r="M7" s="3">
-        <v>1.530370555735256</v>
-      </c>
-      <c r="N7" s="3">
-        <v>1.6145409363006951</v>
-      </c>
-      <c r="O7" s="3">
-        <v>1.6952679831157298</v>
-      </c>
-      <c r="P7" s="3">
-        <v>1.7800313822715164</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>1.8690329513850923</v>
-      </c>
-      <c r="R7" s="3">
-        <v>1.9624845989543469</v>
-      </c>
-      <c r="S7" s="3">
-        <v>2.0606088289020645</v>
-      </c>
-      <c r="T7" s="3">
-        <v>2.1636392703471681</v>
-      </c>
-      <c r="U7" s="3">
-        <v>2.2718212338645265</v>
-      </c>
-      <c r="V7" s="3">
-        <v>2.385412295557753</v>
-      </c>
-      <c r="W7" s="3">
-        <v>2.5046829103356409</v>
-      </c>
-      <c r="X7" s="3">
-        <v>2.629917055852423</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>2.7614129086450441</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>2.8994835540772965</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>3.0444577317811614</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>3.1966806183702197</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>3.356514649288731</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>3.5243403817531678</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>3.7005574008408262</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>3.8855852708828675</v>
-      </c>
-      <c r="AG7" s="3">
-        <v>4.0798645344270108</v>
+      <c r="F7" s="9">
+        <f t="shared" ref="F7:AG7" si="0">E7+F24</f>
+        <v>1.1013723154585875</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.1615304611937896</v>
+      </c>
+      <c r="H7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.215023669651077</v>
+      </c>
+      <c r="I7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.245023669651077</v>
+      </c>
+      <c r="J7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.2850236696510771</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.332023669651077</v>
+      </c>
+      <c r="L7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.3830236696510769</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.4360236696510769</v>
+      </c>
+      <c r="N7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.4910236696510768</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.5460236696510767</v>
+      </c>
+      <c r="P7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.6010236696510767</v>
+      </c>
+      <c r="Q7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.6560236696510766</v>
+      </c>
+      <c r="R7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.7110236696510766</v>
+      </c>
+      <c r="S7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.7660236696510765</v>
+      </c>
+      <c r="T7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.8210236696510764</v>
+      </c>
+      <c r="U7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.8760236696510764</v>
+      </c>
+      <c r="V7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.9310236696510763</v>
+      </c>
+      <c r="W7" s="9">
+        <f t="shared" si="0"/>
+        <v>1.9860236696510762</v>
+      </c>
+      <c r="X7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.0410236696510764</v>
+      </c>
+      <c r="Y7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.0960236696510766</v>
+      </c>
+      <c r="Z7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.1510236696510767</v>
+      </c>
+      <c r="AA7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.2060236696510769</v>
+      </c>
+      <c r="AB7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.261023669651077</v>
+      </c>
+      <c r="AC7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.3160236696510772</v>
+      </c>
+      <c r="AD7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.3710236696510774</v>
+      </c>
+      <c r="AE7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.4260236696510775</v>
+      </c>
+      <c r="AF7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.4810236696510777</v>
+      </c>
+      <c r="AG7" s="9">
+        <f t="shared" si="0"/>
+        <v>2.5360236696510778</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -968,94 +1027,123 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
+        <f>D8+E23</f>
         <v>1.0133978386743965</v>
       </c>
       <c r="F8" s="3">
-        <v>1.0264856204716484</v>
+        <f t="shared" ref="F8:AG8" si="1">E8+F23</f>
+        <v>1.0263125907073904</v>
       </c>
       <c r="G8" s="3">
-        <v>1.0391471697957593</v>
+        <f t="shared" si="1"/>
+        <v>1.0386474437940738</v>
       </c>
       <c r="H8" s="3">
-        <v>1.0514705609449109</v>
+        <f t="shared" si="1"/>
+        <v>1.0505065831992975</v>
       </c>
       <c r="I8" s="3">
-        <v>1.0651396782371947</v>
+        <f t="shared" si="1"/>
+        <v>1.0635065831992974</v>
       </c>
       <c r="J8" s="3">
-        <v>1.0789864940542782</v>
+        <f t="shared" si="1"/>
+        <v>1.0765065831992973</v>
       </c>
       <c r="K8" s="3">
-        <v>1.0930133184769837</v>
+        <f t="shared" si="1"/>
+        <v>1.0895065831992972</v>
       </c>
       <c r="L8" s="3">
-        <v>1.1061294782987074</v>
+        <f t="shared" si="1"/>
+        <v>1.1015065831992972</v>
       </c>
       <c r="M8" s="3">
-        <v>1.1194030320382919</v>
+        <f t="shared" si="1"/>
+        <v>1.1135065831992972</v>
       </c>
       <c r="N8" s="3">
-        <v>1.1328358684227515</v>
+        <f t="shared" si="1"/>
+        <v>1.1255065831992972</v>
       </c>
       <c r="O8" s="3">
-        <v>1.1452970629754016</v>
+        <f t="shared" si="1"/>
+        <v>1.1365065831992971</v>
       </c>
       <c r="P8" s="3">
-        <v>1.1578953306681306</v>
+        <f t="shared" si="1"/>
+        <v>1.1475065831992968</v>
       </c>
       <c r="Q8" s="3">
-        <v>1.1694742839748118</v>
+        <f t="shared" si="1"/>
+        <v>1.1575065831992968</v>
       </c>
       <c r="R8" s="3">
-        <v>1.1811690268145598</v>
+        <f t="shared" si="1"/>
+        <v>1.1675065831992968</v>
       </c>
       <c r="S8" s="3">
-        <v>1.1917995480558907</v>
+        <f t="shared" si="1"/>
+        <v>1.1765065831992967</v>
       </c>
       <c r="T8" s="3">
-        <v>1.2025257439883936</v>
+        <f t="shared" si="1"/>
+        <v>1.1855065831992966</v>
       </c>
       <c r="U8" s="3">
-        <v>1.2133484756842889</v>
+        <f t="shared" si="1"/>
+        <v>1.1945065831992965</v>
       </c>
       <c r="V8" s="3">
-        <v>1.2230552634897633</v>
+        <f t="shared" si="1"/>
+        <v>1.2025065831992965</v>
       </c>
       <c r="W8" s="3">
-        <v>1.2328397055976814</v>
+        <f t="shared" si="1"/>
+        <v>1.2105065831992965</v>
       </c>
       <c r="X8" s="3">
-        <v>1.241469583536865</v>
+        <f t="shared" si="1"/>
+        <v>1.2175065831992964</v>
       </c>
       <c r="Y8" s="3">
-        <v>1.2501598706216228</v>
+        <f t="shared" si="1"/>
+        <v>1.2245065831992963</v>
       </c>
       <c r="Z8" s="3">
-        <v>1.2576608298453527</v>
+        <f t="shared" si="1"/>
+        <v>1.2305065831992963</v>
       </c>
       <c r="AA8" s="3">
-        <v>1.2652067948244248</v>
+        <f t="shared" si="1"/>
+        <v>1.2365065831992963</v>
       </c>
       <c r="AB8" s="3">
-        <v>1.2715328287985468</v>
+        <f t="shared" si="1"/>
+        <v>1.2415065831992962</v>
       </c>
       <c r="AC8" s="3">
-        <v>1.2778904929425394</v>
+        <f t="shared" si="1"/>
+        <v>1.2465065831992961</v>
       </c>
       <c r="AD8" s="3">
-        <v>1.284279945407252</v>
+        <f t="shared" si="1"/>
+        <v>1.251506583199296</v>
       </c>
       <c r="AE8" s="3">
-        <v>1.289417065188881</v>
+        <f t="shared" si="1"/>
+        <v>1.255506583199296</v>
       </c>
       <c r="AF8" s="3">
-        <v>1.2945747334496365</v>
+        <f t="shared" si="1"/>
+        <v>1.259506583199296</v>
       </c>
       <c r="AG8" s="3">
-        <v>1.2984584576499851</v>
+        <f t="shared" si="1"/>
+        <v>1.2625065831992959</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1066,7 +1154,8 @@
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>1.0198019801980198</v>
+        <f>D9+E25</f>
+        <v>1.0374000920039252</v>
       </c>
       <c r="F9" s="3">
         <v>1.0399960788158022</v>
@@ -1153,7 +1242,7 @@
         <v>1.5481447853270867</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -1164,94 +1253,94 @@
         <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>1.05</v>
+        <v>1.0512990110773976</v>
       </c>
       <c r="F10" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.1013723154585875</v>
       </c>
       <c r="G10" s="3">
-        <v>1.1500000000000001</v>
+        <v>1.1615304611937896</v>
       </c>
       <c r="H10" s="3">
-        <v>1.2000000000000002</v>
+        <v>1.215023669651077</v>
       </c>
       <c r="I10" s="3">
-        <v>1.2500000000000002</v>
+        <v>1.245023669651077</v>
       </c>
       <c r="J10" s="3">
-        <v>1.3000000000000003</v>
+        <v>1.2850236696510771</v>
       </c>
       <c r="K10" s="3">
-        <v>1.3500000000000003</v>
+        <v>1.332023669651077</v>
       </c>
       <c r="L10" s="3">
-        <v>1.4000000000000004</v>
+        <v>1.3830236696510769</v>
       </c>
       <c r="M10" s="3">
-        <v>1.4500000000000004</v>
+        <v>1.4360236696510769</v>
       </c>
       <c r="N10" s="3">
-        <v>1.5000000000000004</v>
+        <v>1.4910236696510768</v>
       </c>
       <c r="O10" s="3">
-        <v>1.5500000000000005</v>
+        <v>1.5460236696510767</v>
       </c>
       <c r="P10" s="3">
-        <v>1.6000000000000005</v>
+        <v>1.6010236696510767</v>
       </c>
       <c r="Q10" s="3">
-        <v>1.6500000000000006</v>
+        <v>1.6560236696510766</v>
       </c>
       <c r="R10" s="3">
-        <v>1.7000000000000006</v>
+        <v>1.7110236696510766</v>
       </c>
       <c r="S10" s="3">
-        <v>1.7500000000000007</v>
+        <v>1.7660236696510765</v>
       </c>
       <c r="T10" s="3">
-        <v>1.8000000000000007</v>
+        <v>1.8210236696510764</v>
       </c>
       <c r="U10" s="3">
-        <v>1.8500000000000008</v>
+        <v>1.8760236696510764</v>
       </c>
       <c r="V10" s="3">
-        <v>1.9000000000000008</v>
+        <v>1.9310236696510763</v>
       </c>
       <c r="W10" s="3">
-        <v>1.9500000000000008</v>
+        <v>1.9860236696510762</v>
       </c>
       <c r="X10" s="3">
-        <v>2.0000000000000009</v>
+        <v>2.0410236696510764</v>
       </c>
       <c r="Y10" s="3">
-        <v>2.0500000000000007</v>
+        <v>2.0960236696510766</v>
       </c>
       <c r="Z10" s="3">
-        <v>2.1000000000000005</v>
+        <v>2.1510236696510767</v>
       </c>
       <c r="AA10" s="3">
-        <v>2.1500000000000004</v>
+        <v>2.2060236696510769</v>
       </c>
       <c r="AB10" s="3">
-        <v>2.2000000000000002</v>
+        <v>2.261023669651077</v>
       </c>
       <c r="AC10" s="3">
-        <v>2.25</v>
+        <v>2.3160236696510772</v>
       </c>
       <c r="AD10" s="3">
-        <v>2.2999999999999998</v>
+        <v>2.3710236696510774</v>
       </c>
       <c r="AE10" s="3">
-        <v>2.3499999999999996</v>
+        <v>2.4260236696510775</v>
       </c>
       <c r="AF10" s="3">
-        <v>2.3999999999999995</v>
+        <v>2.4810236696510777</v>
       </c>
       <c r="AG10" s="3">
-        <v>2.4499999999999993</v>
+        <v>2.5360236696510778</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1282,12 +1371,288 @@
       <c r="AF11" s="7"/>
       <c r="AG11" s="7"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
+    </row>
+    <row r="23" spans="3:33" ht="15" x14ac:dyDescent="0.25">
+      <c r="C23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.33978386743964E-2</v>
+      </c>
+      <c r="F23" s="8">
+        <v>1.2914752032993903E-2</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1.2334853086683334E-2</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1.1859139405223745E-2</v>
+      </c>
+      <c r="I23" s="8">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="K23" s="8">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1.2E-2</v>
+      </c>
+      <c r="M23" s="8">
+        <v>1.1999999999999927E-2</v>
+      </c>
+      <c r="N23" s="8">
+        <v>1.2000000000000037E-2</v>
+      </c>
+      <c r="O23" s="8">
+        <v>1.0999999999999984E-2</v>
+      </c>
+      <c r="P23" s="8">
+        <v>1.099999999999976E-2</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>1.0000000000000073E-2</v>
+      </c>
+      <c r="R23" s="8">
+        <v>9.9999999999999863E-3</v>
+      </c>
+      <c r="S23" s="8">
+        <v>8.9999999999999108E-3</v>
+      </c>
+      <c r="T23" s="8">
+        <v>8.9999999999998068E-3</v>
+      </c>
+      <c r="U23" s="8">
+        <v>8.9999999999998258E-3</v>
+      </c>
+      <c r="V23" s="8">
+        <v>8.0000000000000106E-3</v>
+      </c>
+      <c r="W23" s="8">
+        <v>7.9999999999999499E-3</v>
+      </c>
+      <c r="X23" s="8">
+        <v>6.9999999999998553E-3</v>
+      </c>
+      <c r="Y23" s="8">
+        <v>6.9999999999998371E-3</v>
+      </c>
+      <c r="Z23" s="8">
+        <v>6.000000000000053E-3</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>6.0000000000000851E-3</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>4.9999999999998527E-3</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>4.9999999999999333E-3</v>
+      </c>
+      <c r="AD23" s="8">
+        <v>4.9999999999997919E-3</v>
+      </c>
+      <c r="AE23" s="8">
+        <v>3.9999999999999281E-3</v>
+      </c>
+      <c r="AF23" s="8">
+        <v>3.9999999999999957E-3</v>
+      </c>
+      <c r="AG23" s="8">
+        <v>2.9999999999998695E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" ht="15" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="8">
+        <v>5.1299011077397663E-2</v>
+      </c>
+      <c r="F24" s="8">
+        <v>5.0073304381189863E-2</v>
+      </c>
+      <c r="G24" s="8">
+        <v>6.0158145735202055E-2</v>
+      </c>
+      <c r="H24" s="8">
+        <v>5.3493208457287535E-2</v>
+      </c>
+      <c r="I24" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="K24" s="8">
+        <v>4.7E-2</v>
+      </c>
+      <c r="L24" s="8">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M24" s="8">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="N24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="O24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="P24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="R24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="S24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="T24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="U24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="V24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="W24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="X24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="Y24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="Z24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AC24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AD24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AE24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AF24" s="8">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AG24" s="8">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" ht="15" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3.7400092003925196E-2</v>
+      </c>
+      <c r="F25" s="8">
+        <v>3.66847775428445E-2</v>
+      </c>
+      <c r="G25" s="8">
+        <v>4.7240586948776836E-2</v>
+      </c>
+      <c r="H25" s="8">
+        <v>4.1146111578867037E-2</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="O25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="R25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="S25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="T25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="U25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="V25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="W25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="X25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="Y25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AA25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AB25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AC25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AD25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AE25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AF25" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="AG25" s="8">
+        <v>0.04</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
